--- a/artfynd/A 56872-2021 artfynd.xlsx
+++ b/artfynd/A 56872-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56872-2021 artfynd.xlsx
+++ b/artfynd/A 56872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97220276</v>
+        <v>97216912</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arvika, Vrm</t>
+          <t>Humlekil Blåbärshaget, Arvika, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365791.3479639904</v>
+        <v>365745</v>
       </c>
       <c r="R2" t="n">
-        <v>6609039.631188712</v>
+        <v>6608884</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +744,9 @@
           <t>2021-11-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97216004</v>
+        <v>3057802</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,19 +801,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arvika, Vrm</t>
+          <t>Södervik, ca 250 m O om, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365760.0656318347</v>
+        <v>365769</v>
       </c>
       <c r="R3" t="n">
-        <v>6609073.179603136</v>
+        <v>6609057</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,24 +845,24 @@
           <t>Arvika</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>S-Arv-0404</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-12-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-12-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>90 bladrosetter med 35 blomstänglar, spridda kring gammal körväg-stig i öst-västlig riktning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,31 +873,40 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog med enstaka granar</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Värmland Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elvi Eriksson, Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97216061</v>
+        <v>97216004</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365757.8729010922</v>
+        <v>365761</v>
       </c>
       <c r="R4" t="n">
-        <v>6609026.136153462</v>
+        <v>6609073</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,19 +973,9 @@
           <t>2021-11-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3057802</v>
+        <v>97216061</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,26 +1030,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södervik, ca 250 m O om, Vrm</t>
+          <t>Arvika, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365769.1350070951</v>
+        <v>365758</v>
       </c>
       <c r="R5" t="n">
-        <v>6609057.147470426</v>
+        <v>6609026</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,34 +1067,14 @@
           <t>Arvika</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>S-Arv-0404</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-12-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-12-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>90 bladrosetter med 35 blomstänglar, spridda kring gammal körväg-stig i öst-västlig riktning</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,33 +1085,217 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>hällmarkstallskog med enstaka granar</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Värmland Floraväktarna</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvi Eriksson, Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97216720</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Humlekil Gläntan, Humlekil Blåbärshaget, Arvika, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>365727</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6608885</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97220118</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arvika, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>365792</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6609039</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
